--- a/cea765fb-________.xlsx
+++ b/cea765fb-________.xlsx
@@ -19,10 +19,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d;@"/>
-    <numFmt numFmtId="165" formatCode="0&quot;年度&quot;"/>
-    <numFmt numFmtId="166" formatCode="0&quot;月度&quot;"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -77,7 +75,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -94,12 +92,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.3499862666707358"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -198,7 +190,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -257,10 +249,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -354,46 +342,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>auto</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0">
-      <text>
-        <t>ここに年(西暦)を入力</t>
-      </text>
-    </comment>
-    <comment ref="C2" authorId="0" shapeId="0">
-      <text>
-        <t>ここに月を入力すると、タイトルと日付・土日の色が自動で変わります</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>auto</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0">
-      <text>
-        <t>ここに年(西暦)を入力</t>
-      </text>
-    </comment>
-    <comment ref="C2" authorId="0" shapeId="0">
-      <text>
-        <t>ここに月を入力すると、タイトルと日付・土日の色が自動で変わります</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -726,9 +674,10 @@
   </cols>
   <sheetData>
     <row r="1" ht="32.5" customHeight="1" s="19">
-      <c r="A1" s="2">
-        <f>"　"&amp;C2&amp;"月度　安全改善確認シート"</f>
-        <v/>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3月度　安全改善確認シート</t>
+        </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
         <is>
@@ -737,25 +686,24 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="n">
-        <v>2026</v>
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>2026年度</t>
+        </is>
       </c>
       <c r="B2" s="18" t="inlineStr">
         <is>
           <t>目標：１件以上/月</t>
         </is>
       </c>
-      <c r="C2" s="21" t="n">
-        <v>3</v>
-      </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
           <t>改善：土屋(幸)/確認：社長</t>
         </is>
       </c>
-      <c r="E2" s="22" t="n"/>
-      <c r="F2" s="22" t="n"/>
-      <c r="G2" s="22" t="n"/>
+      <c r="E2" s="20" t="n"/>
+      <c r="F2" s="20" t="n"/>
+      <c r="G2" s="20" t="n"/>
     </row>
     <row r="3" ht="35.25" customHeight="1" s="19">
       <c r="A3" s="10" t="inlineStr">
@@ -773,8 +721,8 @@
           <t>改　　善</t>
         </is>
       </c>
-      <c r="D3" s="23" t="n"/>
-      <c r="E3" s="24" t="n"/>
+      <c r="D3" s="21" t="n"/>
+      <c r="E3" s="22" t="n"/>
       <c r="F3" s="10" t="inlineStr">
         <is>
           <t>完了日</t>
@@ -788,14 +736,14 @@
       </c>
     </row>
     <row r="4" ht="21" customHeight="1" s="19">
-      <c r="A4" s="25">
-        <f>DATE($A$2,$C$2,1)</f>
+      <c r="A4" s="23">
+        <f>DATE(VALUE(LEFT($A$2,FIND("年度",$A$2)-1)),VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),1)</f>
         <v/>
       </c>
       <c r="B4" s="15" t="n"/>
       <c r="C4" s="14" t="n"/>
-      <c r="D4" s="23" t="n"/>
-      <c r="E4" s="23" t="n"/>
+      <c r="D4" s="21" t="n"/>
+      <c r="E4" s="21" t="n"/>
       <c r="F4" s="16" t="inlineStr">
         <is>
           <t>/</t>
@@ -804,14 +752,14 @@
       <c r="G4" s="16" t="n"/>
     </row>
     <row r="5" ht="21" customHeight="1" s="19">
-      <c r="A5" s="26">
-        <f>IF($A4="","",IF(MONTH($A4+1)=$C$2,$A4+1,""))</f>
+      <c r="A5" s="24">
+        <f>IF($A4="","",IF(MONTH($A4+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A4+1,""))</f>
         <v/>
       </c>
       <c r="B5" s="9" t="n"/>
       <c r="C5" s="8" t="n"/>
-      <c r="D5" s="23" t="n"/>
-      <c r="E5" s="23" t="n"/>
+      <c r="D5" s="21" t="n"/>
+      <c r="E5" s="21" t="n"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -820,14 +768,14 @@
       <c r="G5" s="4" t="n"/>
     </row>
     <row r="6" ht="21" customHeight="1" s="19">
-      <c r="A6" s="26">
-        <f>IF($A5="","",IF(MONTH($A5+1)=$C$2,$A5+1,""))</f>
+      <c r="A6" s="24">
+        <f>IF($A5="","",IF(MONTH($A5+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A5+1,""))</f>
         <v/>
       </c>
       <c r="B6" s="9" t="n"/>
       <c r="C6" s="8" t="n"/>
-      <c r="D6" s="23" t="n"/>
-      <c r="E6" s="23" t="n"/>
+      <c r="D6" s="21" t="n"/>
+      <c r="E6" s="21" t="n"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -836,14 +784,14 @@
       <c r="G6" s="4" t="n"/>
     </row>
     <row r="7" ht="21" customHeight="1" s="19">
-      <c r="A7" s="26">
-        <f>IF($A6="","",IF(MONTH($A6+1)=$C$2,$A6+1,""))</f>
+      <c r="A7" s="24">
+        <f>IF($A6="","",IF(MONTH($A6+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A6+1,""))</f>
         <v/>
       </c>
       <c r="B7" s="9" t="n"/>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="23" t="n"/>
-      <c r="E7" s="23" t="n"/>
+      <c r="D7" s="21" t="n"/>
+      <c r="E7" s="21" t="n"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -852,14 +800,14 @@
       <c r="G7" s="4" t="n"/>
     </row>
     <row r="8" ht="21" customHeight="1" s="19">
-      <c r="A8" s="26">
-        <f>IF($A7="","",IF(MONTH($A7+1)=$C$2,$A7+1,""))</f>
+      <c r="A8" s="24">
+        <f>IF($A7="","",IF(MONTH($A7+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A7+1,""))</f>
         <v/>
       </c>
       <c r="B8" s="9" t="n"/>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="23" t="n"/>
-      <c r="E8" s="23" t="n"/>
+      <c r="D8" s="21" t="n"/>
+      <c r="E8" s="21" t="n"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -868,14 +816,14 @@
       <c r="G8" s="4" t="n"/>
     </row>
     <row r="9" ht="21" customHeight="1" s="19">
-      <c r="A9" s="26">
-        <f>IF($A8="","",IF(MONTH($A8+1)=$C$2,$A8+1,""))</f>
+      <c r="A9" s="24">
+        <f>IF($A8="","",IF(MONTH($A8+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A8+1,""))</f>
         <v/>
       </c>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="23" t="n"/>
-      <c r="E9" s="23" t="n"/>
+      <c r="D9" s="21" t="n"/>
+      <c r="E9" s="21" t="n"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -884,14 +832,14 @@
       <c r="G9" s="4" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1" s="19">
-      <c r="A10" s="25">
-        <f>IF($A9="","",IF(MONTH($A9+1)=$C$2,$A9+1,""))</f>
+      <c r="A10" s="23">
+        <f>IF($A9="","",IF(MONTH($A9+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A9+1,""))</f>
         <v/>
       </c>
       <c r="B10" s="15" t="n"/>
       <c r="C10" s="14" t="n"/>
-      <c r="D10" s="23" t="n"/>
-      <c r="E10" s="23" t="n"/>
+      <c r="D10" s="21" t="n"/>
+      <c r="E10" s="21" t="n"/>
       <c r="F10" s="16" t="inlineStr">
         <is>
           <t>/</t>
@@ -900,14 +848,14 @@
       <c r="G10" s="16" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1" s="19">
-      <c r="A11" s="25">
-        <f>IF($A10="","",IF(MONTH($A10+1)=$C$2,$A10+1,""))</f>
+      <c r="A11" s="23">
+        <f>IF($A10="","",IF(MONTH($A10+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A10+1,""))</f>
         <v/>
       </c>
       <c r="B11" s="15" t="n"/>
       <c r="C11" s="14" t="n"/>
-      <c r="D11" s="23" t="n"/>
-      <c r="E11" s="23" t="n"/>
+      <c r="D11" s="21" t="n"/>
+      <c r="E11" s="21" t="n"/>
       <c r="F11" s="16" t="inlineStr">
         <is>
           <t>/</t>
@@ -916,14 +864,14 @@
       <c r="G11" s="16" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="19">
-      <c r="A12" s="26">
-        <f>IF($A11="","",IF(MONTH($A11+1)=$C$2,$A11+1,""))</f>
+      <c r="A12" s="24">
+        <f>IF($A11="","",IF(MONTH($A11+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A11+1,""))</f>
         <v/>
       </c>
       <c r="B12" s="9" t="n"/>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="23" t="n"/>
-      <c r="E12" s="23" t="n"/>
+      <c r="D12" s="21" t="n"/>
+      <c r="E12" s="21" t="n"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -932,14 +880,14 @@
       <c r="G12" s="4" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="19">
-      <c r="A13" s="26">
-        <f>IF($A12="","",IF(MONTH($A12+1)=$C$2,$A12+1,""))</f>
+      <c r="A13" s="24">
+        <f>IF($A12="","",IF(MONTH($A12+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A12+1,""))</f>
         <v/>
       </c>
       <c r="B13" s="9" t="n"/>
       <c r="C13" s="8" t="n"/>
-      <c r="D13" s="23" t="n"/>
-      <c r="E13" s="23" t="n"/>
+      <c r="D13" s="21" t="n"/>
+      <c r="E13" s="21" t="n"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -948,14 +896,14 @@
       <c r="G13" s="4" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1" s="19">
-      <c r="A14" s="26">
-        <f>IF($A13="","",IF(MONTH($A13+1)=$C$2,$A13+1,""))</f>
+      <c r="A14" s="24">
+        <f>IF($A13="","",IF(MONTH($A13+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A13+1,""))</f>
         <v/>
       </c>
       <c r="B14" s="9" t="n"/>
       <c r="C14" s="8" t="n"/>
-      <c r="D14" s="23" t="n"/>
-      <c r="E14" s="23" t="n"/>
+      <c r="D14" s="21" t="n"/>
+      <c r="E14" s="21" t="n"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -964,14 +912,14 @@
       <c r="G14" s="4" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1" s="19">
-      <c r="A15" s="26">
-        <f>IF($A14="","",IF(MONTH($A14+1)=$C$2,$A14+1,""))</f>
+      <c r="A15" s="24">
+        <f>IF($A14="","",IF(MONTH($A14+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A14+1,""))</f>
         <v/>
       </c>
       <c r="B15" s="9" t="n"/>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="23" t="n"/>
-      <c r="E15" s="23" t="n"/>
+      <c r="D15" s="21" t="n"/>
+      <c r="E15" s="21" t="n"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -980,14 +928,14 @@
       <c r="G15" s="4" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1" s="19">
-      <c r="A16" s="26">
-        <f>IF($A15="","",IF(MONTH($A15+1)=$C$2,$A15+1,""))</f>
+      <c r="A16" s="24">
+        <f>IF($A15="","",IF(MONTH($A15+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A15+1,""))</f>
         <v/>
       </c>
       <c r="B16" s="9" t="n"/>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="23" t="n"/>
-      <c r="E16" s="23" t="n"/>
+      <c r="D16" s="21" t="n"/>
+      <c r="E16" s="21" t="n"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -996,14 +944,14 @@
       <c r="G16" s="4" t="n"/>
     </row>
     <row r="17" ht="21" customHeight="1" s="19">
-      <c r="A17" s="25">
-        <f>IF($A16="","",IF(MONTH($A16+1)=$C$2,$A16+1,""))</f>
+      <c r="A17" s="23">
+        <f>IF($A16="","",IF(MONTH($A16+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A16+1,""))</f>
         <v/>
       </c>
       <c r="B17" s="15" t="n"/>
       <c r="C17" s="14" t="n"/>
-      <c r="D17" s="23" t="n"/>
-      <c r="E17" s="23" t="n"/>
+      <c r="D17" s="21" t="n"/>
+      <c r="E17" s="21" t="n"/>
       <c r="F17" s="16" t="inlineStr">
         <is>
           <t>/</t>
@@ -1012,14 +960,14 @@
       <c r="G17" s="16" t="n"/>
     </row>
     <row r="18" ht="21" customHeight="1" s="19">
-      <c r="A18" s="25">
-        <f>IF($A17="","",IF(MONTH($A17+1)=$C$2,$A17+1,""))</f>
+      <c r="A18" s="23">
+        <f>IF($A17="","",IF(MONTH($A17+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A17+1,""))</f>
         <v/>
       </c>
       <c r="B18" s="15" t="n"/>
       <c r="C18" s="14" t="n"/>
-      <c r="D18" s="23" t="n"/>
-      <c r="E18" s="23" t="n"/>
+      <c r="D18" s="21" t="n"/>
+      <c r="E18" s="21" t="n"/>
       <c r="F18" s="16" t="inlineStr">
         <is>
           <t>/</t>
@@ -1028,14 +976,14 @@
       <c r="G18" s="16" t="n"/>
     </row>
     <row r="19" ht="21" customHeight="1" s="19">
-      <c r="A19" s="26">
-        <f>IF($A18="","",IF(MONTH($A18+1)=$C$2,$A18+1,""))</f>
+      <c r="A19" s="24">
+        <f>IF($A18="","",IF(MONTH($A18+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A18+1,""))</f>
         <v/>
       </c>
       <c r="B19" s="9" t="n"/>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="23" t="n"/>
-      <c r="E19" s="23" t="n"/>
+      <c r="D19" s="21" t="n"/>
+      <c r="E19" s="21" t="n"/>
       <c r="F19" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1044,14 +992,14 @@
       <c r="G19" s="4" t="n"/>
     </row>
     <row r="20" ht="21" customHeight="1" s="19">
-      <c r="A20" s="26">
-        <f>IF($A19="","",IF(MONTH($A19+1)=$C$2,$A19+1,""))</f>
+      <c r="A20" s="24">
+        <f>IF($A19="","",IF(MONTH($A19+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A19+1,""))</f>
         <v/>
       </c>
       <c r="B20" s="9" t="n"/>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="23" t="n"/>
-      <c r="E20" s="23" t="n"/>
+      <c r="D20" s="21" t="n"/>
+      <c r="E20" s="21" t="n"/>
       <c r="F20" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1060,14 +1008,14 @@
       <c r="G20" s="4" t="n"/>
     </row>
     <row r="21" ht="21" customHeight="1" s="19">
-      <c r="A21" s="26">
-        <f>IF($A20="","",IF(MONTH($A20+1)=$C$2,$A20+1,""))</f>
+      <c r="A21" s="24">
+        <f>IF($A20="","",IF(MONTH($A20+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A20+1,""))</f>
         <v/>
       </c>
       <c r="B21" s="9" t="n"/>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="23" t="n"/>
-      <c r="E21" s="23" t="n"/>
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="21" t="n"/>
       <c r="F21" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1076,14 +1024,14 @@
       <c r="G21" s="4" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1" s="19">
-      <c r="A22" s="26">
-        <f>IF($A21="","",IF(MONTH($A21+1)=$C$2,$A21+1,""))</f>
+      <c r="A22" s="24">
+        <f>IF($A21="","",IF(MONTH($A21+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A21+1,""))</f>
         <v/>
       </c>
       <c r="B22" s="9" t="n"/>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="23" t="n"/>
-      <c r="E22" s="23" t="n"/>
+      <c r="D22" s="21" t="n"/>
+      <c r="E22" s="21" t="n"/>
       <c r="F22" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1092,14 +1040,14 @@
       <c r="G22" s="4" t="n"/>
     </row>
     <row r="23" ht="21" customHeight="1" s="19">
-      <c r="A23" s="26">
-        <f>IF($A22="","",IF(MONTH($A22+1)=$C$2,$A22+1,""))</f>
+      <c r="A23" s="24">
+        <f>IF($A22="","",IF(MONTH($A22+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A22+1,""))</f>
         <v/>
       </c>
       <c r="B23" s="9" t="n"/>
       <c r="C23" s="8" t="n"/>
-      <c r="D23" s="23" t="n"/>
-      <c r="E23" s="23" t="n"/>
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="21" t="n"/>
       <c r="F23" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1108,14 +1056,14 @@
       <c r="G23" s="4" t="n"/>
     </row>
     <row r="24" ht="21" customHeight="1" s="19">
-      <c r="A24" s="25">
-        <f>IF($A23="","",IF(MONTH($A23+1)=$C$2,$A23+1,""))</f>
+      <c r="A24" s="23">
+        <f>IF($A23="","",IF(MONTH($A23+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A23+1,""))</f>
         <v/>
       </c>
       <c r="B24" s="15" t="n"/>
       <c r="C24" s="14" t="n"/>
-      <c r="D24" s="23" t="n"/>
-      <c r="E24" s="23" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="21" t="n"/>
       <c r="F24" s="16" t="inlineStr">
         <is>
           <t>/</t>
@@ -1124,14 +1072,14 @@
       <c r="G24" s="16" t="n"/>
     </row>
     <row r="25" ht="21" customHeight="1" s="19">
-      <c r="A25" s="25">
-        <f>IF($A24="","",IF(MONTH($A24+1)=$C$2,$A24+1,""))</f>
+      <c r="A25" s="23">
+        <f>IF($A24="","",IF(MONTH($A24+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A24+1,""))</f>
         <v/>
       </c>
       <c r="B25" s="15" t="n"/>
       <c r="C25" s="14" t="n"/>
-      <c r="D25" s="23" t="n"/>
-      <c r="E25" s="23" t="n"/>
+      <c r="D25" s="21" t="n"/>
+      <c r="E25" s="21" t="n"/>
       <c r="F25" s="16" t="inlineStr">
         <is>
           <t>/</t>
@@ -1140,14 +1088,14 @@
       <c r="G25" s="16" t="n"/>
     </row>
     <row r="26" ht="21" customHeight="1" s="19">
-      <c r="A26" s="26">
-        <f>IF($A25="","",IF(MONTH($A25+1)=$C$2,$A25+1,""))</f>
+      <c r="A26" s="24">
+        <f>IF($A25="","",IF(MONTH($A25+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A25+1,""))</f>
         <v/>
       </c>
       <c r="B26" s="9" t="n"/>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="23" t="n"/>
-      <c r="E26" s="23" t="n"/>
+      <c r="D26" s="21" t="n"/>
+      <c r="E26" s="21" t="n"/>
       <c r="F26" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1156,14 +1104,14 @@
       <c r="G26" s="4" t="n"/>
     </row>
     <row r="27" ht="21" customHeight="1" s="19">
-      <c r="A27" s="26">
-        <f>IF($A26="","",IF(MONTH($A26+1)=$C$2,$A26+1,""))</f>
+      <c r="A27" s="24">
+        <f>IF($A26="","",IF(MONTH($A26+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A26+1,""))</f>
         <v/>
       </c>
       <c r="B27" s="9" t="n"/>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="23" t="n"/>
-      <c r="E27" s="23" t="n"/>
+      <c r="D27" s="21" t="n"/>
+      <c r="E27" s="21" t="n"/>
       <c r="F27" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1172,14 +1120,14 @@
       <c r="G27" s="4" t="n"/>
     </row>
     <row r="28" ht="21" customHeight="1" s="19">
-      <c r="A28" s="26">
-        <f>IF($A27="","",IF(MONTH($A27+1)=$C$2,$A27+1,""))</f>
+      <c r="A28" s="24">
+        <f>IF($A27="","",IF(MONTH($A27+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A27+1,""))</f>
         <v/>
       </c>
       <c r="B28" s="9" t="n"/>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="23" t="n"/>
-      <c r="E28" s="23" t="n"/>
+      <c r="D28" s="21" t="n"/>
+      <c r="E28" s="21" t="n"/>
       <c r="F28" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1188,14 +1136,14 @@
       <c r="G28" s="4" t="n"/>
     </row>
     <row r="29" ht="21" customHeight="1" s="19">
-      <c r="A29" s="26">
-        <f>IF($A28="","",IF(MONTH($A28+1)=$C$2,$A28+1,""))</f>
+      <c r="A29" s="24">
+        <f>IF($A28="","",IF(MONTH($A28+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A28+1,""))</f>
         <v/>
       </c>
       <c r="B29" s="9" t="n"/>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="23" t="n"/>
-      <c r="E29" s="23" t="n"/>
+      <c r="D29" s="21" t="n"/>
+      <c r="E29" s="21" t="n"/>
       <c r="F29" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1204,14 +1152,14 @@
       <c r="G29" s="4" t="n"/>
     </row>
     <row r="30" ht="21" customHeight="1" s="19">
-      <c r="A30" s="26">
-        <f>IF($A29="","",IF(MONTH($A29+1)=$C$2,$A29+1,""))</f>
+      <c r="A30" s="24">
+        <f>IF($A29="","",IF(MONTH($A29+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A29+1,""))</f>
         <v/>
       </c>
       <c r="B30" s="9" t="n"/>
       <c r="C30" s="8" t="n"/>
-      <c r="D30" s="23" t="n"/>
-      <c r="E30" s="23" t="n"/>
+      <c r="D30" s="21" t="n"/>
+      <c r="E30" s="21" t="n"/>
       <c r="F30" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1220,14 +1168,14 @@
       <c r="G30" s="4" t="n"/>
     </row>
     <row r="31" ht="21" customHeight="1" s="19">
-      <c r="A31" s="25">
-        <f>IF($A30="","",IF(MONTH($A30+1)=$C$2,$A30+1,""))</f>
+      <c r="A31" s="23">
+        <f>IF($A30="","",IF(MONTH($A30+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A30+1,""))</f>
         <v/>
       </c>
       <c r="B31" s="15" t="n"/>
       <c r="C31" s="14" t="n"/>
-      <c r="D31" s="23" t="n"/>
-      <c r="E31" s="23" t="n"/>
+      <c r="D31" s="21" t="n"/>
+      <c r="E31" s="21" t="n"/>
       <c r="F31" s="16" t="inlineStr">
         <is>
           <t>/</t>
@@ -1236,14 +1184,14 @@
       <c r="G31" s="16" t="n"/>
     </row>
     <row r="32" ht="21" customHeight="1" s="19">
-      <c r="A32" s="25">
-        <f>IF($A31="","",IF(MONTH($A31+1)=$C$2,$A31+1,""))</f>
+      <c r="A32" s="23">
+        <f>IF($A31="","",IF(MONTH($A31+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A31+1,""))</f>
         <v/>
       </c>
       <c r="B32" s="15" t="n"/>
       <c r="C32" s="14" t="n"/>
-      <c r="D32" s="23" t="n"/>
-      <c r="E32" s="23" t="n"/>
+      <c r="D32" s="21" t="n"/>
+      <c r="E32" s="21" t="n"/>
       <c r="F32" s="16" t="inlineStr">
         <is>
           <t>/</t>
@@ -1252,14 +1200,14 @@
       <c r="G32" s="16" t="n"/>
     </row>
     <row r="33" ht="21" customHeight="1" s="19">
-      <c r="A33" s="26">
-        <f>IF($A32="","",IF(MONTH($A32+1)=$C$2,$A32+1,""))</f>
+      <c r="A33" s="24">
+        <f>IF($A32="","",IF(MONTH($A32+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A32+1,""))</f>
         <v/>
       </c>
       <c r="B33" s="9" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="23" t="n"/>
-      <c r="E33" s="23" t="n"/>
+      <c r="D33" s="21" t="n"/>
+      <c r="E33" s="21" t="n"/>
       <c r="F33" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1268,14 +1216,14 @@
       <c r="G33" s="4" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="26">
-        <f>IF($A33="","",IF(MONTH($A33+1)=$C$2,$A33+1,""))</f>
+      <c r="A34" s="24">
+        <f>IF($A33="","",IF(MONTH($A33+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A33+1,""))</f>
         <v/>
       </c>
       <c r="B34" s="9" t="n"/>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="23" t="n"/>
-      <c r="E34" s="23" t="n"/>
+      <c r="D34" s="21" t="n"/>
+      <c r="E34" s="21" t="n"/>
       <c r="F34" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1328,7 +1276,6 @@
   <printOptions verticalCentered="1"/>
   <pageMargins left="0.8267716535433072" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1347,9 +1294,10 @@
   </cols>
   <sheetData>
     <row r="1" ht="32.5" customHeight="1" s="19">
-      <c r="A1" s="2">
-        <f>"　"&amp;C2&amp;"月度　安全改善確認シート"</f>
-        <v/>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3月度　安全改善確認シート</t>
+        </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
         <is>
@@ -1358,25 +1306,24 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="n">
-        <v>2026</v>
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>2026年度</t>
+        </is>
       </c>
       <c r="B2" s="18" t="inlineStr">
         <is>
           <t>目標：１件以上/月</t>
         </is>
       </c>
-      <c r="C2" s="21" t="n">
-        <v>3</v>
-      </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
           <t>改善：上村/確認：社長</t>
         </is>
       </c>
-      <c r="E2" s="22" t="n"/>
-      <c r="F2" s="22" t="n"/>
-      <c r="G2" s="22" t="n"/>
+      <c r="E2" s="20" t="n"/>
+      <c r="F2" s="20" t="n"/>
+      <c r="G2" s="20" t="n"/>
     </row>
     <row r="3" ht="35.25" customHeight="1" s="19">
       <c r="A3" s="10" t="inlineStr">
@@ -1394,8 +1341,8 @@
           <t>改　　善</t>
         </is>
       </c>
-      <c r="D3" s="23" t="n"/>
-      <c r="E3" s="24" t="n"/>
+      <c r="D3" s="21" t="n"/>
+      <c r="E3" s="22" t="n"/>
       <c r="F3" s="10" t="inlineStr">
         <is>
           <t>完了日</t>
@@ -1409,14 +1356,14 @@
       </c>
     </row>
     <row r="4" ht="21" customHeight="1" s="19">
-      <c r="A4" s="25">
-        <f>DATE($A$2,$C$2,1)</f>
+      <c r="A4" s="23">
+        <f>DATE(VALUE(LEFT($A$2,FIND("年度",$A$2)-1)),VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),1)</f>
         <v/>
       </c>
       <c r="B4" s="15" t="n"/>
       <c r="C4" s="14" t="n"/>
-      <c r="D4" s="23" t="n"/>
-      <c r="E4" s="23" t="n"/>
+      <c r="D4" s="21" t="n"/>
+      <c r="E4" s="21" t="n"/>
       <c r="F4" s="16" t="inlineStr">
         <is>
           <t>/</t>
@@ -1425,14 +1372,14 @@
       <c r="G4" s="16" t="n"/>
     </row>
     <row r="5" ht="21" customHeight="1" s="19">
-      <c r="A5" s="26">
-        <f>IF($A4="","",IF(MONTH($A4+1)=$C$2,$A4+1,""))</f>
+      <c r="A5" s="24">
+        <f>IF($A4="","",IF(MONTH($A4+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A4+1,""))</f>
         <v/>
       </c>
       <c r="B5" s="9" t="n"/>
       <c r="C5" s="8" t="n"/>
-      <c r="D5" s="23" t="n"/>
-      <c r="E5" s="23" t="n"/>
+      <c r="D5" s="21" t="n"/>
+      <c r="E5" s="21" t="n"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1441,14 +1388,14 @@
       <c r="G5" s="4" t="n"/>
     </row>
     <row r="6" ht="21" customHeight="1" s="19">
-      <c r="A6" s="26">
-        <f>IF($A5="","",IF(MONTH($A5+1)=$C$2,$A5+1,""))</f>
+      <c r="A6" s="24">
+        <f>IF($A5="","",IF(MONTH($A5+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A5+1,""))</f>
         <v/>
       </c>
       <c r="B6" s="9" t="n"/>
       <c r="C6" s="8" t="n"/>
-      <c r="D6" s="23" t="n"/>
-      <c r="E6" s="23" t="n"/>
+      <c r="D6" s="21" t="n"/>
+      <c r="E6" s="21" t="n"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1457,14 +1404,14 @@
       <c r="G6" s="4" t="n"/>
     </row>
     <row r="7" ht="21" customHeight="1" s="19">
-      <c r="A7" s="26">
-        <f>IF($A6="","",IF(MONTH($A6+1)=$C$2,$A6+1,""))</f>
+      <c r="A7" s="24">
+        <f>IF($A6="","",IF(MONTH($A6+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A6+1,""))</f>
         <v/>
       </c>
       <c r="B7" s="9" t="n"/>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="23" t="n"/>
-      <c r="E7" s="23" t="n"/>
+      <c r="D7" s="21" t="n"/>
+      <c r="E7" s="21" t="n"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1473,14 +1420,14 @@
       <c r="G7" s="4" t="n"/>
     </row>
     <row r="8" ht="21" customHeight="1" s="19">
-      <c r="A8" s="26">
-        <f>IF($A7="","",IF(MONTH($A7+1)=$C$2,$A7+1,""))</f>
+      <c r="A8" s="24">
+        <f>IF($A7="","",IF(MONTH($A7+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A7+1,""))</f>
         <v/>
       </c>
       <c r="B8" s="9" t="n"/>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="23" t="n"/>
-      <c r="E8" s="23" t="n"/>
+      <c r="D8" s="21" t="n"/>
+      <c r="E8" s="21" t="n"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1489,14 +1436,14 @@
       <c r="G8" s="4" t="n"/>
     </row>
     <row r="9" ht="21" customHeight="1" s="19">
-      <c r="A9" s="26">
-        <f>IF($A8="","",IF(MONTH($A8+1)=$C$2,$A8+1,""))</f>
+      <c r="A9" s="24">
+        <f>IF($A8="","",IF(MONTH($A8+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A8+1,""))</f>
         <v/>
       </c>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="23" t="n"/>
-      <c r="E9" s="23" t="n"/>
+      <c r="D9" s="21" t="n"/>
+      <c r="E9" s="21" t="n"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1505,14 +1452,14 @@
       <c r="G9" s="4" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1" s="19">
-      <c r="A10" s="25">
-        <f>IF($A9="","",IF(MONTH($A9+1)=$C$2,$A9+1,""))</f>
+      <c r="A10" s="23">
+        <f>IF($A9="","",IF(MONTH($A9+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A9+1,""))</f>
         <v/>
       </c>
       <c r="B10" s="15" t="n"/>
       <c r="C10" s="14" t="n"/>
-      <c r="D10" s="23" t="n"/>
-      <c r="E10" s="23" t="n"/>
+      <c r="D10" s="21" t="n"/>
+      <c r="E10" s="21" t="n"/>
       <c r="F10" s="16" t="inlineStr">
         <is>
           <t>/</t>
@@ -1521,14 +1468,14 @@
       <c r="G10" s="16" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1" s="19">
-      <c r="A11" s="25">
-        <f>IF($A10="","",IF(MONTH($A10+1)=$C$2,$A10+1,""))</f>
+      <c r="A11" s="23">
+        <f>IF($A10="","",IF(MONTH($A10+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A10+1,""))</f>
         <v/>
       </c>
       <c r="B11" s="15" t="n"/>
       <c r="C11" s="14" t="n"/>
-      <c r="D11" s="23" t="n"/>
-      <c r="E11" s="23" t="n"/>
+      <c r="D11" s="21" t="n"/>
+      <c r="E11" s="21" t="n"/>
       <c r="F11" s="16" t="inlineStr">
         <is>
           <t>/</t>
@@ -1537,14 +1484,14 @@
       <c r="G11" s="16" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="19">
-      <c r="A12" s="26">
-        <f>IF($A11="","",IF(MONTH($A11+1)=$C$2,$A11+1,""))</f>
+      <c r="A12" s="24">
+        <f>IF($A11="","",IF(MONTH($A11+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A11+1,""))</f>
         <v/>
       </c>
       <c r="B12" s="9" t="n"/>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="23" t="n"/>
-      <c r="E12" s="23" t="n"/>
+      <c r="D12" s="21" t="n"/>
+      <c r="E12" s="21" t="n"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1553,14 +1500,14 @@
       <c r="G12" s="4" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="19">
-      <c r="A13" s="26">
-        <f>IF($A12="","",IF(MONTH($A12+1)=$C$2,$A12+1,""))</f>
+      <c r="A13" s="24">
+        <f>IF($A12="","",IF(MONTH($A12+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A12+1,""))</f>
         <v/>
       </c>
       <c r="B13" s="9" t="n"/>
       <c r="C13" s="8" t="n"/>
-      <c r="D13" s="23" t="n"/>
-      <c r="E13" s="23" t="n"/>
+      <c r="D13" s="21" t="n"/>
+      <c r="E13" s="21" t="n"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1569,14 +1516,14 @@
       <c r="G13" s="4" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1" s="19">
-      <c r="A14" s="26">
-        <f>IF($A13="","",IF(MONTH($A13+1)=$C$2,$A13+1,""))</f>
+      <c r="A14" s="24">
+        <f>IF($A13="","",IF(MONTH($A13+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A13+1,""))</f>
         <v/>
       </c>
       <c r="B14" s="9" t="n"/>
       <c r="C14" s="8" t="n"/>
-      <c r="D14" s="23" t="n"/>
-      <c r="E14" s="23" t="n"/>
+      <c r="D14" s="21" t="n"/>
+      <c r="E14" s="21" t="n"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1585,14 +1532,14 @@
       <c r="G14" s="4" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1" s="19">
-      <c r="A15" s="26">
-        <f>IF($A14="","",IF(MONTH($A14+1)=$C$2,$A14+1,""))</f>
+      <c r="A15" s="24">
+        <f>IF($A14="","",IF(MONTH($A14+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A14+1,""))</f>
         <v/>
       </c>
       <c r="B15" s="9" t="n"/>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="23" t="n"/>
-      <c r="E15" s="23" t="n"/>
+      <c r="D15" s="21" t="n"/>
+      <c r="E15" s="21" t="n"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1601,14 +1548,14 @@
       <c r="G15" s="4" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1" s="19">
-      <c r="A16" s="26">
-        <f>IF($A15="","",IF(MONTH($A15+1)=$C$2,$A15+1,""))</f>
+      <c r="A16" s="24">
+        <f>IF($A15="","",IF(MONTH($A15+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A15+1,""))</f>
         <v/>
       </c>
       <c r="B16" s="9" t="n"/>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="23" t="n"/>
-      <c r="E16" s="23" t="n"/>
+      <c r="D16" s="21" t="n"/>
+      <c r="E16" s="21" t="n"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1617,14 +1564,14 @@
       <c r="G16" s="4" t="n"/>
     </row>
     <row r="17" ht="21" customHeight="1" s="19">
-      <c r="A17" s="25">
-        <f>IF($A16="","",IF(MONTH($A16+1)=$C$2,$A16+1,""))</f>
+      <c r="A17" s="23">
+        <f>IF($A16="","",IF(MONTH($A16+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A16+1,""))</f>
         <v/>
       </c>
       <c r="B17" s="15" t="n"/>
       <c r="C17" s="14" t="n"/>
-      <c r="D17" s="23" t="n"/>
-      <c r="E17" s="23" t="n"/>
+      <c r="D17" s="21" t="n"/>
+      <c r="E17" s="21" t="n"/>
       <c r="F17" s="16" t="inlineStr">
         <is>
           <t>/</t>
@@ -1633,14 +1580,14 @@
       <c r="G17" s="16" t="n"/>
     </row>
     <row r="18" ht="21" customHeight="1" s="19">
-      <c r="A18" s="25">
-        <f>IF($A17="","",IF(MONTH($A17+1)=$C$2,$A17+1,""))</f>
+      <c r="A18" s="23">
+        <f>IF($A17="","",IF(MONTH($A17+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A17+1,""))</f>
         <v/>
       </c>
       <c r="B18" s="15" t="n"/>
       <c r="C18" s="14" t="n"/>
-      <c r="D18" s="23" t="n"/>
-      <c r="E18" s="23" t="n"/>
+      <c r="D18" s="21" t="n"/>
+      <c r="E18" s="21" t="n"/>
       <c r="F18" s="16" t="inlineStr">
         <is>
           <t>/</t>
@@ -1649,14 +1596,14 @@
       <c r="G18" s="16" t="n"/>
     </row>
     <row r="19" ht="21" customHeight="1" s="19">
-      <c r="A19" s="26">
-        <f>IF($A18="","",IF(MONTH($A18+1)=$C$2,$A18+1,""))</f>
+      <c r="A19" s="24">
+        <f>IF($A18="","",IF(MONTH($A18+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A18+1,""))</f>
         <v/>
       </c>
       <c r="B19" s="9" t="n"/>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="23" t="n"/>
-      <c r="E19" s="23" t="n"/>
+      <c r="D19" s="21" t="n"/>
+      <c r="E19" s="21" t="n"/>
       <c r="F19" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1665,14 +1612,14 @@
       <c r="G19" s="4" t="n"/>
     </row>
     <row r="20" ht="21" customHeight="1" s="19">
-      <c r="A20" s="26">
-        <f>IF($A19="","",IF(MONTH($A19+1)=$C$2,$A19+1,""))</f>
+      <c r="A20" s="24">
+        <f>IF($A19="","",IF(MONTH($A19+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A19+1,""))</f>
         <v/>
       </c>
       <c r="B20" s="9" t="n"/>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="23" t="n"/>
-      <c r="E20" s="23" t="n"/>
+      <c r="D20" s="21" t="n"/>
+      <c r="E20" s="21" t="n"/>
       <c r="F20" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1681,14 +1628,14 @@
       <c r="G20" s="4" t="n"/>
     </row>
     <row r="21" ht="21" customHeight="1" s="19">
-      <c r="A21" s="26">
-        <f>IF($A20="","",IF(MONTH($A20+1)=$C$2,$A20+1,""))</f>
+      <c r="A21" s="24">
+        <f>IF($A20="","",IF(MONTH($A20+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A20+1,""))</f>
         <v/>
       </c>
       <c r="B21" s="9" t="n"/>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="23" t="n"/>
-      <c r="E21" s="23" t="n"/>
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="21" t="n"/>
       <c r="F21" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1697,14 +1644,14 @@
       <c r="G21" s="4" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1" s="19">
-      <c r="A22" s="26">
-        <f>IF($A21="","",IF(MONTH($A21+1)=$C$2,$A21+1,""))</f>
+      <c r="A22" s="24">
+        <f>IF($A21="","",IF(MONTH($A21+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A21+1,""))</f>
         <v/>
       </c>
       <c r="B22" s="9" t="n"/>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="23" t="n"/>
-      <c r="E22" s="23" t="n"/>
+      <c r="D22" s="21" t="n"/>
+      <c r="E22" s="21" t="n"/>
       <c r="F22" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1713,14 +1660,14 @@
       <c r="G22" s="4" t="n"/>
     </row>
     <row r="23" ht="21" customHeight="1" s="19">
-      <c r="A23" s="26">
-        <f>IF($A22="","",IF(MONTH($A22+1)=$C$2,$A22+1,""))</f>
+      <c r="A23" s="24">
+        <f>IF($A22="","",IF(MONTH($A22+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A22+1,""))</f>
         <v/>
       </c>
       <c r="B23" s="9" t="n"/>
       <c r="C23" s="8" t="n"/>
-      <c r="D23" s="23" t="n"/>
-      <c r="E23" s="23" t="n"/>
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="21" t="n"/>
       <c r="F23" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1729,14 +1676,14 @@
       <c r="G23" s="4" t="n"/>
     </row>
     <row r="24" ht="21" customHeight="1" s="19">
-      <c r="A24" s="25">
-        <f>IF($A23="","",IF(MONTH($A23+1)=$C$2,$A23+1,""))</f>
+      <c r="A24" s="23">
+        <f>IF($A23="","",IF(MONTH($A23+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A23+1,""))</f>
         <v/>
       </c>
       <c r="B24" s="15" t="n"/>
       <c r="C24" s="14" t="n"/>
-      <c r="D24" s="23" t="n"/>
-      <c r="E24" s="23" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="21" t="n"/>
       <c r="F24" s="16" t="inlineStr">
         <is>
           <t>/</t>
@@ -1745,14 +1692,14 @@
       <c r="G24" s="16" t="n"/>
     </row>
     <row r="25" ht="21" customHeight="1" s="19">
-      <c r="A25" s="25">
-        <f>IF($A24="","",IF(MONTH($A24+1)=$C$2,$A24+1,""))</f>
+      <c r="A25" s="23">
+        <f>IF($A24="","",IF(MONTH($A24+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A24+1,""))</f>
         <v/>
       </c>
       <c r="B25" s="15" t="n"/>
       <c r="C25" s="14" t="n"/>
-      <c r="D25" s="23" t="n"/>
-      <c r="E25" s="23" t="n"/>
+      <c r="D25" s="21" t="n"/>
+      <c r="E25" s="21" t="n"/>
       <c r="F25" s="16" t="inlineStr">
         <is>
           <t>/</t>
@@ -1761,14 +1708,14 @@
       <c r="G25" s="16" t="n"/>
     </row>
     <row r="26" ht="21" customHeight="1" s="19">
-      <c r="A26" s="26">
-        <f>IF($A25="","",IF(MONTH($A25+1)=$C$2,$A25+1,""))</f>
+      <c r="A26" s="24">
+        <f>IF($A25="","",IF(MONTH($A25+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A25+1,""))</f>
         <v/>
       </c>
       <c r="B26" s="9" t="n"/>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="23" t="n"/>
-      <c r="E26" s="23" t="n"/>
+      <c r="D26" s="21" t="n"/>
+      <c r="E26" s="21" t="n"/>
       <c r="F26" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1777,14 +1724,14 @@
       <c r="G26" s="4" t="n"/>
     </row>
     <row r="27" ht="21" customHeight="1" s="19">
-      <c r="A27" s="26">
-        <f>IF($A26="","",IF(MONTH($A26+1)=$C$2,$A26+1,""))</f>
+      <c r="A27" s="24">
+        <f>IF($A26="","",IF(MONTH($A26+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A26+1,""))</f>
         <v/>
       </c>
       <c r="B27" s="9" t="n"/>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="23" t="n"/>
-      <c r="E27" s="23" t="n"/>
+      <c r="D27" s="21" t="n"/>
+      <c r="E27" s="21" t="n"/>
       <c r="F27" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1793,14 +1740,14 @@
       <c r="G27" s="4" t="n"/>
     </row>
     <row r="28" ht="21" customHeight="1" s="19">
-      <c r="A28" s="26">
-        <f>IF($A27="","",IF(MONTH($A27+1)=$C$2,$A27+1,""))</f>
+      <c r="A28" s="24">
+        <f>IF($A27="","",IF(MONTH($A27+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A27+1,""))</f>
         <v/>
       </c>
       <c r="B28" s="9" t="n"/>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="23" t="n"/>
-      <c r="E28" s="23" t="n"/>
+      <c r="D28" s="21" t="n"/>
+      <c r="E28" s="21" t="n"/>
       <c r="F28" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1809,14 +1756,14 @@
       <c r="G28" s="4" t="n"/>
     </row>
     <row r="29" ht="21" customHeight="1" s="19">
-      <c r="A29" s="26">
-        <f>IF($A28="","",IF(MONTH($A28+1)=$C$2,$A28+1,""))</f>
+      <c r="A29" s="24">
+        <f>IF($A28="","",IF(MONTH($A28+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A28+1,""))</f>
         <v/>
       </c>
       <c r="B29" s="9" t="n"/>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="23" t="n"/>
-      <c r="E29" s="23" t="n"/>
+      <c r="D29" s="21" t="n"/>
+      <c r="E29" s="21" t="n"/>
       <c r="F29" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1825,14 +1772,14 @@
       <c r="G29" s="4" t="n"/>
     </row>
     <row r="30" ht="21" customHeight="1" s="19">
-      <c r="A30" s="26">
-        <f>IF($A29="","",IF(MONTH($A29+1)=$C$2,$A29+1,""))</f>
+      <c r="A30" s="24">
+        <f>IF($A29="","",IF(MONTH($A29+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A29+1,""))</f>
         <v/>
       </c>
       <c r="B30" s="9" t="n"/>
       <c r="C30" s="8" t="n"/>
-      <c r="D30" s="23" t="n"/>
-      <c r="E30" s="23" t="n"/>
+      <c r="D30" s="21" t="n"/>
+      <c r="E30" s="21" t="n"/>
       <c r="F30" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1841,14 +1788,14 @@
       <c r="G30" s="4" t="n"/>
     </row>
     <row r="31" ht="21" customHeight="1" s="19">
-      <c r="A31" s="25">
-        <f>IF($A30="","",IF(MONTH($A30+1)=$C$2,$A30+1,""))</f>
+      <c r="A31" s="23">
+        <f>IF($A30="","",IF(MONTH($A30+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A30+1,""))</f>
         <v/>
       </c>
       <c r="B31" s="15" t="n"/>
       <c r="C31" s="14" t="n"/>
-      <c r="D31" s="23" t="n"/>
-      <c r="E31" s="23" t="n"/>
+      <c r="D31" s="21" t="n"/>
+      <c r="E31" s="21" t="n"/>
       <c r="F31" s="16" t="inlineStr">
         <is>
           <t>/</t>
@@ -1857,14 +1804,14 @@
       <c r="G31" s="16" t="n"/>
     </row>
     <row r="32" ht="21" customHeight="1" s="19">
-      <c r="A32" s="25">
-        <f>IF($A31="","",IF(MONTH($A31+1)=$C$2,$A31+1,""))</f>
+      <c r="A32" s="23">
+        <f>IF($A31="","",IF(MONTH($A31+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A31+1,""))</f>
         <v/>
       </c>
       <c r="B32" s="15" t="n"/>
       <c r="C32" s="14" t="n"/>
-      <c r="D32" s="23" t="n"/>
-      <c r="E32" s="23" t="n"/>
+      <c r="D32" s="21" t="n"/>
+      <c r="E32" s="21" t="n"/>
       <c r="F32" s="16" t="inlineStr">
         <is>
           <t>/</t>
@@ -1873,14 +1820,14 @@
       <c r="G32" s="16" t="n"/>
     </row>
     <row r="33" ht="21" customHeight="1" s="19">
-      <c r="A33" s="26">
-        <f>IF($A32="","",IF(MONTH($A32+1)=$C$2,$A32+1,""))</f>
+      <c r="A33" s="24">
+        <f>IF($A32="","",IF(MONTH($A32+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A32+1,""))</f>
         <v/>
       </c>
       <c r="B33" s="9" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="23" t="n"/>
-      <c r="E33" s="23" t="n"/>
+      <c r="D33" s="21" t="n"/>
+      <c r="E33" s="21" t="n"/>
       <c r="F33" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1889,14 +1836,14 @@
       <c r="G33" s="4" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="26">
-        <f>IF($A33="","",IF(MONTH($A33+1)=$C$2,$A33+1,""))</f>
+      <c r="A34" s="24">
+        <f>IF($A33="","",IF(MONTH($A33+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A33+1,""))</f>
         <v/>
       </c>
       <c r="B34" s="9" t="n"/>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="23" t="n"/>
-      <c r="E34" s="23" t="n"/>
+      <c r="D34" s="21" t="n"/>
+      <c r="E34" s="21" t="n"/>
       <c r="F34" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1949,6 +1896,5 @@
   <printOptions verticalCentered="1"/>
   <pageMargins left="0.8267716535433072" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/cea765fb-________.xlsx
+++ b/cea765fb-________.xlsx
@@ -252,12 +252,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -740,26 +738,26 @@
         <f>DATE(VALUE(LEFT($A$2,FIND("年度",$A$2)-1)),VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),1)</f>
         <v/>
       </c>
-      <c r="B4" s="15" t="n"/>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="21" t="n"/>
-      <c r="E4" s="21" t="n"/>
-      <c r="F4" s="16" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="G4" s="16" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="24" t="n"/>
+      <c r="E4" s="24" t="n"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n"/>
     </row>
     <row r="5" ht="21" customHeight="1" s="19">
-      <c r="A5" s="24">
+      <c r="A5" s="23">
         <f>IF($A4="","",IF(MONTH($A4+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A4+1,""))</f>
         <v/>
       </c>
       <c r="B5" s="9" t="n"/>
       <c r="C5" s="8" t="n"/>
-      <c r="D5" s="21" t="n"/>
-      <c r="E5" s="21" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -768,14 +766,14 @@
       <c r="G5" s="4" t="n"/>
     </row>
     <row r="6" ht="21" customHeight="1" s="19">
-      <c r="A6" s="24">
+      <c r="A6" s="23">
         <f>IF($A5="","",IF(MONTH($A5+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A5+1,""))</f>
         <v/>
       </c>
       <c r="B6" s="9" t="n"/>
       <c r="C6" s="8" t="n"/>
-      <c r="D6" s="21" t="n"/>
-      <c r="E6" s="21" t="n"/>
+      <c r="D6" s="24" t="n"/>
+      <c r="E6" s="24" t="n"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -784,14 +782,14 @@
       <c r="G6" s="4" t="n"/>
     </row>
     <row r="7" ht="21" customHeight="1" s="19">
-      <c r="A7" s="24">
+      <c r="A7" s="23">
         <f>IF($A6="","",IF(MONTH($A6+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A6+1,""))</f>
         <v/>
       </c>
       <c r="B7" s="9" t="n"/>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="21" t="n"/>
-      <c r="E7" s="21" t="n"/>
+      <c r="D7" s="24" t="n"/>
+      <c r="E7" s="24" t="n"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -800,14 +798,14 @@
       <c r="G7" s="4" t="n"/>
     </row>
     <row r="8" ht="21" customHeight="1" s="19">
-      <c r="A8" s="24">
+      <c r="A8" s="23">
         <f>IF($A7="","",IF(MONTH($A7+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A7+1,""))</f>
         <v/>
       </c>
       <c r="B8" s="9" t="n"/>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="21" t="n"/>
-      <c r="E8" s="21" t="n"/>
+      <c r="D8" s="24" t="n"/>
+      <c r="E8" s="24" t="n"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -816,14 +814,14 @@
       <c r="G8" s="4" t="n"/>
     </row>
     <row r="9" ht="21" customHeight="1" s="19">
-      <c r="A9" s="24">
+      <c r="A9" s="23">
         <f>IF($A8="","",IF(MONTH($A8+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A8+1,""))</f>
         <v/>
       </c>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="21" t="n"/>
-      <c r="E9" s="21" t="n"/>
+      <c r="D9" s="24" t="n"/>
+      <c r="E9" s="24" t="n"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -836,42 +834,42 @@
         <f>IF($A9="","",IF(MONTH($A9+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A9+1,""))</f>
         <v/>
       </c>
-      <c r="B10" s="15" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="21" t="n"/>
-      <c r="E10" s="21" t="n"/>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="24" t="n"/>
+      <c r="E10" s="24" t="n"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1" s="19">
       <c r="A11" s="23">
         <f>IF($A10="","",IF(MONTH($A10+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A10+1,""))</f>
         <v/>
       </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="21" t="n"/>
-      <c r="E11" s="21" t="n"/>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="19">
-      <c r="A12" s="24">
+      <c r="A12" s="23">
         <f>IF($A11="","",IF(MONTH($A11+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A11+1,""))</f>
         <v/>
       </c>
       <c r="B12" s="9" t="n"/>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="21" t="n"/>
-      <c r="E12" s="21" t="n"/>
+      <c r="D12" s="24" t="n"/>
+      <c r="E12" s="24" t="n"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -880,14 +878,14 @@
       <c r="G12" s="4" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="19">
-      <c r="A13" s="24">
+      <c r="A13" s="23">
         <f>IF($A12="","",IF(MONTH($A12+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A12+1,""))</f>
         <v/>
       </c>
       <c r="B13" s="9" t="n"/>
       <c r="C13" s="8" t="n"/>
-      <c r="D13" s="21" t="n"/>
-      <c r="E13" s="21" t="n"/>
+      <c r="D13" s="24" t="n"/>
+      <c r="E13" s="24" t="n"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -896,14 +894,14 @@
       <c r="G13" s="4" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1" s="19">
-      <c r="A14" s="24">
+      <c r="A14" s="23">
         <f>IF($A13="","",IF(MONTH($A13+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A13+1,""))</f>
         <v/>
       </c>
       <c r="B14" s="9" t="n"/>
       <c r="C14" s="8" t="n"/>
-      <c r="D14" s="21" t="n"/>
-      <c r="E14" s="21" t="n"/>
+      <c r="D14" s="24" t="n"/>
+      <c r="E14" s="24" t="n"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -912,14 +910,14 @@
       <c r="G14" s="4" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1" s="19">
-      <c r="A15" s="24">
+      <c r="A15" s="23">
         <f>IF($A14="","",IF(MONTH($A14+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A14+1,""))</f>
         <v/>
       </c>
       <c r="B15" s="9" t="n"/>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="21" t="n"/>
-      <c r="E15" s="21" t="n"/>
+      <c r="D15" s="24" t="n"/>
+      <c r="E15" s="24" t="n"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -928,14 +926,14 @@
       <c r="G15" s="4" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1" s="19">
-      <c r="A16" s="24">
+      <c r="A16" s="23">
         <f>IF($A15="","",IF(MONTH($A15+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A15+1,""))</f>
         <v/>
       </c>
       <c r="B16" s="9" t="n"/>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="21" t="n"/>
-      <c r="E16" s="21" t="n"/>
+      <c r="D16" s="24" t="n"/>
+      <c r="E16" s="24" t="n"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -948,42 +946,42 @@
         <f>IF($A16="","",IF(MONTH($A16+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A16+1,""))</f>
         <v/>
       </c>
-      <c r="B17" s="15" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="21" t="n"/>
-      <c r="E17" s="21" t="n"/>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="24" t="n"/>
+      <c r="E17" s="24" t="n"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n"/>
     </row>
     <row r="18" ht="21" customHeight="1" s="19">
       <c r="A18" s="23">
         <f>IF($A17="","",IF(MONTH($A17+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A17+1,""))</f>
         <v/>
       </c>
-      <c r="B18" s="15" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="21" t="n"/>
-      <c r="E18" s="21" t="n"/>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="24" t="n"/>
+      <c r="E18" s="24" t="n"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n"/>
     </row>
     <row r="19" ht="21" customHeight="1" s="19">
-      <c r="A19" s="24">
+      <c r="A19" s="23">
         <f>IF($A18="","",IF(MONTH($A18+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A18+1,""))</f>
         <v/>
       </c>
       <c r="B19" s="9" t="n"/>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="21" t="n"/>
-      <c r="E19" s="21" t="n"/>
+      <c r="D19" s="24" t="n"/>
+      <c r="E19" s="24" t="n"/>
       <c r="F19" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -992,14 +990,14 @@
       <c r="G19" s="4" t="n"/>
     </row>
     <row r="20" ht="21" customHeight="1" s="19">
-      <c r="A20" s="24">
+      <c r="A20" s="23">
         <f>IF($A19="","",IF(MONTH($A19+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A19+1,""))</f>
         <v/>
       </c>
       <c r="B20" s="9" t="n"/>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="21" t="n"/>
-      <c r="E20" s="21" t="n"/>
+      <c r="D20" s="24" t="n"/>
+      <c r="E20" s="24" t="n"/>
       <c r="F20" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1008,14 +1006,14 @@
       <c r="G20" s="4" t="n"/>
     </row>
     <row r="21" ht="21" customHeight="1" s="19">
-      <c r="A21" s="24">
+      <c r="A21" s="23">
         <f>IF($A20="","",IF(MONTH($A20+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A20+1,""))</f>
         <v/>
       </c>
       <c r="B21" s="9" t="n"/>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="21" t="n"/>
-      <c r="E21" s="21" t="n"/>
+      <c r="D21" s="24" t="n"/>
+      <c r="E21" s="24" t="n"/>
       <c r="F21" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1024,14 +1022,14 @@
       <c r="G21" s="4" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1" s="19">
-      <c r="A22" s="24">
+      <c r="A22" s="23">
         <f>IF($A21="","",IF(MONTH($A21+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A21+1,""))</f>
         <v/>
       </c>
       <c r="B22" s="9" t="n"/>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="21" t="n"/>
-      <c r="E22" s="21" t="n"/>
+      <c r="D22" s="24" t="n"/>
+      <c r="E22" s="24" t="n"/>
       <c r="F22" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1040,14 +1038,14 @@
       <c r="G22" s="4" t="n"/>
     </row>
     <row r="23" ht="21" customHeight="1" s="19">
-      <c r="A23" s="24">
+      <c r="A23" s="23">
         <f>IF($A22="","",IF(MONTH($A22+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A22+1,""))</f>
         <v/>
       </c>
       <c r="B23" s="9" t="n"/>
       <c r="C23" s="8" t="n"/>
-      <c r="D23" s="21" t="n"/>
-      <c r="E23" s="21" t="n"/>
+      <c r="D23" s="24" t="n"/>
+      <c r="E23" s="24" t="n"/>
       <c r="F23" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1060,42 +1058,42 @@
         <f>IF($A23="","",IF(MONTH($A23+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A23+1,""))</f>
         <v/>
       </c>
-      <c r="B24" s="15" t="n"/>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="21" t="n"/>
-      <c r="E24" s="21" t="n"/>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="24" t="n"/>
+      <c r="E24" s="24" t="n"/>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n"/>
     </row>
     <row r="25" ht="21" customHeight="1" s="19">
       <c r="A25" s="23">
         <f>IF($A24="","",IF(MONTH($A24+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A24+1,""))</f>
         <v/>
       </c>
-      <c r="B25" s="15" t="n"/>
-      <c r="C25" s="14" t="n"/>
-      <c r="D25" s="21" t="n"/>
-      <c r="E25" s="21" t="n"/>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="24" t="n"/>
+      <c r="E25" s="24" t="n"/>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n"/>
     </row>
     <row r="26" ht="21" customHeight="1" s="19">
-      <c r="A26" s="24">
+      <c r="A26" s="23">
         <f>IF($A25="","",IF(MONTH($A25+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A25+1,""))</f>
         <v/>
       </c>
       <c r="B26" s="9" t="n"/>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="21" t="n"/>
-      <c r="E26" s="21" t="n"/>
+      <c r="D26" s="24" t="n"/>
+      <c r="E26" s="24" t="n"/>
       <c r="F26" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1104,14 +1102,14 @@
       <c r="G26" s="4" t="n"/>
     </row>
     <row r="27" ht="21" customHeight="1" s="19">
-      <c r="A27" s="24">
+      <c r="A27" s="23">
         <f>IF($A26="","",IF(MONTH($A26+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A26+1,""))</f>
         <v/>
       </c>
       <c r="B27" s="9" t="n"/>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="21" t="n"/>
-      <c r="E27" s="21" t="n"/>
+      <c r="D27" s="24" t="n"/>
+      <c r="E27" s="24" t="n"/>
       <c r="F27" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1120,14 +1118,14 @@
       <c r="G27" s="4" t="n"/>
     </row>
     <row r="28" ht="21" customHeight="1" s="19">
-      <c r="A28" s="24">
+      <c r="A28" s="23">
         <f>IF($A27="","",IF(MONTH($A27+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A27+1,""))</f>
         <v/>
       </c>
       <c r="B28" s="9" t="n"/>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="21" t="n"/>
-      <c r="E28" s="21" t="n"/>
+      <c r="D28" s="24" t="n"/>
+      <c r="E28" s="24" t="n"/>
       <c r="F28" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1136,14 +1134,14 @@
       <c r="G28" s="4" t="n"/>
     </row>
     <row r="29" ht="21" customHeight="1" s="19">
-      <c r="A29" s="24">
+      <c r="A29" s="23">
         <f>IF($A28="","",IF(MONTH($A28+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A28+1,""))</f>
         <v/>
       </c>
       <c r="B29" s="9" t="n"/>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="21" t="n"/>
-      <c r="E29" s="21" t="n"/>
+      <c r="D29" s="24" t="n"/>
+      <c r="E29" s="24" t="n"/>
       <c r="F29" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1152,14 +1150,14 @@
       <c r="G29" s="4" t="n"/>
     </row>
     <row r="30" ht="21" customHeight="1" s="19">
-      <c r="A30" s="24">
+      <c r="A30" s="23">
         <f>IF($A29="","",IF(MONTH($A29+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A29+1,""))</f>
         <v/>
       </c>
       <c r="B30" s="9" t="n"/>
       <c r="C30" s="8" t="n"/>
-      <c r="D30" s="21" t="n"/>
-      <c r="E30" s="21" t="n"/>
+      <c r="D30" s="24" t="n"/>
+      <c r="E30" s="24" t="n"/>
       <c r="F30" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1172,42 +1170,42 @@
         <f>IF($A30="","",IF(MONTH($A30+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A30+1,""))</f>
         <v/>
       </c>
-      <c r="B31" s="15" t="n"/>
-      <c r="C31" s="14" t="n"/>
-      <c r="D31" s="21" t="n"/>
-      <c r="E31" s="21" t="n"/>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="G31" s="16" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="24" t="n"/>
+      <c r="E31" s="24" t="n"/>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n"/>
     </row>
     <row r="32" ht="21" customHeight="1" s="19">
       <c r="A32" s="23">
         <f>IF($A31="","",IF(MONTH($A31+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A31+1,""))</f>
         <v/>
       </c>
-      <c r="B32" s="15" t="n"/>
-      <c r="C32" s="14" t="n"/>
-      <c r="D32" s="21" t="n"/>
-      <c r="E32" s="21" t="n"/>
-      <c r="F32" s="16" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="n"/>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="24" t="n"/>
+      <c r="E32" s="24" t="n"/>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n"/>
     </row>
     <row r="33" ht="21" customHeight="1" s="19">
-      <c r="A33" s="24">
+      <c r="A33" s="23">
         <f>IF($A32="","",IF(MONTH($A32+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A32+1,""))</f>
         <v/>
       </c>
       <c r="B33" s="9" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="21" t="n"/>
-      <c r="E33" s="21" t="n"/>
+      <c r="D33" s="24" t="n"/>
+      <c r="E33" s="24" t="n"/>
       <c r="F33" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1216,14 +1214,14 @@
       <c r="G33" s="4" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="24">
+      <c r="A34" s="23">
         <f>IF($A33="","",IF(MONTH($A33+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A33+1,""))</f>
         <v/>
       </c>
       <c r="B34" s="9" t="n"/>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="21" t="n"/>
-      <c r="E34" s="21" t="n"/>
+      <c r="D34" s="24" t="n"/>
+      <c r="E34" s="24" t="n"/>
       <c r="F34" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1360,26 +1358,26 @@
         <f>DATE(VALUE(LEFT($A$2,FIND("年度",$A$2)-1)),VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),1)</f>
         <v/>
       </c>
-      <c r="B4" s="15" t="n"/>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="21" t="n"/>
-      <c r="E4" s="21" t="n"/>
-      <c r="F4" s="16" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="G4" s="16" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="24" t="n"/>
+      <c r="E4" s="24" t="n"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n"/>
     </row>
     <row r="5" ht="21" customHeight="1" s="19">
-      <c r="A5" s="24">
+      <c r="A5" s="23">
         <f>IF($A4="","",IF(MONTH($A4+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A4+1,""))</f>
         <v/>
       </c>
       <c r="B5" s="9" t="n"/>
       <c r="C5" s="8" t="n"/>
-      <c r="D5" s="21" t="n"/>
-      <c r="E5" s="21" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1388,14 +1386,14 @@
       <c r="G5" s="4" t="n"/>
     </row>
     <row r="6" ht="21" customHeight="1" s="19">
-      <c r="A6" s="24">
+      <c r="A6" s="23">
         <f>IF($A5="","",IF(MONTH($A5+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A5+1,""))</f>
         <v/>
       </c>
       <c r="B6" s="9" t="n"/>
       <c r="C6" s="8" t="n"/>
-      <c r="D6" s="21" t="n"/>
-      <c r="E6" s="21" t="n"/>
+      <c r="D6" s="24" t="n"/>
+      <c r="E6" s="24" t="n"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1404,14 +1402,14 @@
       <c r="G6" s="4" t="n"/>
     </row>
     <row r="7" ht="21" customHeight="1" s="19">
-      <c r="A7" s="24">
+      <c r="A7" s="23">
         <f>IF($A6="","",IF(MONTH($A6+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A6+1,""))</f>
         <v/>
       </c>
       <c r="B7" s="9" t="n"/>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="21" t="n"/>
-      <c r="E7" s="21" t="n"/>
+      <c r="D7" s="24" t="n"/>
+      <c r="E7" s="24" t="n"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1420,14 +1418,14 @@
       <c r="G7" s="4" t="n"/>
     </row>
     <row r="8" ht="21" customHeight="1" s="19">
-      <c r="A8" s="24">
+      <c r="A8" s="23">
         <f>IF($A7="","",IF(MONTH($A7+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A7+1,""))</f>
         <v/>
       </c>
       <c r="B8" s="9" t="n"/>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="21" t="n"/>
-      <c r="E8" s="21" t="n"/>
+      <c r="D8" s="24" t="n"/>
+      <c r="E8" s="24" t="n"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1436,14 +1434,14 @@
       <c r="G8" s="4" t="n"/>
     </row>
     <row r="9" ht="21" customHeight="1" s="19">
-      <c r="A9" s="24">
+      <c r="A9" s="23">
         <f>IF($A8="","",IF(MONTH($A8+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A8+1,""))</f>
         <v/>
       </c>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="21" t="n"/>
-      <c r="E9" s="21" t="n"/>
+      <c r="D9" s="24" t="n"/>
+      <c r="E9" s="24" t="n"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1456,42 +1454,42 @@
         <f>IF($A9="","",IF(MONTH($A9+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A9+1,""))</f>
         <v/>
       </c>
-      <c r="B10" s="15" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="21" t="n"/>
-      <c r="E10" s="21" t="n"/>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="24" t="n"/>
+      <c r="E10" s="24" t="n"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1" s="19">
       <c r="A11" s="23">
         <f>IF($A10="","",IF(MONTH($A10+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A10+1,""))</f>
         <v/>
       </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="21" t="n"/>
-      <c r="E11" s="21" t="n"/>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="19">
-      <c r="A12" s="24">
+      <c r="A12" s="23">
         <f>IF($A11="","",IF(MONTH($A11+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A11+1,""))</f>
         <v/>
       </c>
       <c r="B12" s="9" t="n"/>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="21" t="n"/>
-      <c r="E12" s="21" t="n"/>
+      <c r="D12" s="24" t="n"/>
+      <c r="E12" s="24" t="n"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1500,14 +1498,14 @@
       <c r="G12" s="4" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="19">
-      <c r="A13" s="24">
+      <c r="A13" s="23">
         <f>IF($A12="","",IF(MONTH($A12+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A12+1,""))</f>
         <v/>
       </c>
       <c r="B13" s="9" t="n"/>
       <c r="C13" s="8" t="n"/>
-      <c r="D13" s="21" t="n"/>
-      <c r="E13" s="21" t="n"/>
+      <c r="D13" s="24" t="n"/>
+      <c r="E13" s="24" t="n"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1516,14 +1514,14 @@
       <c r="G13" s="4" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1" s="19">
-      <c r="A14" s="24">
+      <c r="A14" s="23">
         <f>IF($A13="","",IF(MONTH($A13+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A13+1,""))</f>
         <v/>
       </c>
       <c r="B14" s="9" t="n"/>
       <c r="C14" s="8" t="n"/>
-      <c r="D14" s="21" t="n"/>
-      <c r="E14" s="21" t="n"/>
+      <c r="D14" s="24" t="n"/>
+      <c r="E14" s="24" t="n"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1532,14 +1530,14 @@
       <c r="G14" s="4" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1" s="19">
-      <c r="A15" s="24">
+      <c r="A15" s="23">
         <f>IF($A14="","",IF(MONTH($A14+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A14+1,""))</f>
         <v/>
       </c>
       <c r="B15" s="9" t="n"/>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="21" t="n"/>
-      <c r="E15" s="21" t="n"/>
+      <c r="D15" s="24" t="n"/>
+      <c r="E15" s="24" t="n"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1548,14 +1546,14 @@
       <c r="G15" s="4" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1" s="19">
-      <c r="A16" s="24">
+      <c r="A16" s="23">
         <f>IF($A15="","",IF(MONTH($A15+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A15+1,""))</f>
         <v/>
       </c>
       <c r="B16" s="9" t="n"/>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="21" t="n"/>
-      <c r="E16" s="21" t="n"/>
+      <c r="D16" s="24" t="n"/>
+      <c r="E16" s="24" t="n"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1568,42 +1566,42 @@
         <f>IF($A16="","",IF(MONTH($A16+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A16+1,""))</f>
         <v/>
       </c>
-      <c r="B17" s="15" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="21" t="n"/>
-      <c r="E17" s="21" t="n"/>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="24" t="n"/>
+      <c r="E17" s="24" t="n"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n"/>
     </row>
     <row r="18" ht="21" customHeight="1" s="19">
       <c r="A18" s="23">
         <f>IF($A17="","",IF(MONTH($A17+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A17+1,""))</f>
         <v/>
       </c>
-      <c r="B18" s="15" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="21" t="n"/>
-      <c r="E18" s="21" t="n"/>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="24" t="n"/>
+      <c r="E18" s="24" t="n"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n"/>
     </row>
     <row r="19" ht="21" customHeight="1" s="19">
-      <c r="A19" s="24">
+      <c r="A19" s="23">
         <f>IF($A18="","",IF(MONTH($A18+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A18+1,""))</f>
         <v/>
       </c>
       <c r="B19" s="9" t="n"/>
       <c r="C19" s="8" t="n"/>
-      <c r="D19" s="21" t="n"/>
-      <c r="E19" s="21" t="n"/>
+      <c r="D19" s="24" t="n"/>
+      <c r="E19" s="24" t="n"/>
       <c r="F19" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1612,14 +1610,14 @@
       <c r="G19" s="4" t="n"/>
     </row>
     <row r="20" ht="21" customHeight="1" s="19">
-      <c r="A20" s="24">
+      <c r="A20" s="23">
         <f>IF($A19="","",IF(MONTH($A19+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A19+1,""))</f>
         <v/>
       </c>
       <c r="B20" s="9" t="n"/>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="21" t="n"/>
-      <c r="E20" s="21" t="n"/>
+      <c r="D20" s="24" t="n"/>
+      <c r="E20" s="24" t="n"/>
       <c r="F20" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1628,14 +1626,14 @@
       <c r="G20" s="4" t="n"/>
     </row>
     <row r="21" ht="21" customHeight="1" s="19">
-      <c r="A21" s="24">
+      <c r="A21" s="23">
         <f>IF($A20="","",IF(MONTH($A20+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A20+1,""))</f>
         <v/>
       </c>
       <c r="B21" s="9" t="n"/>
       <c r="C21" s="8" t="n"/>
-      <c r="D21" s="21" t="n"/>
-      <c r="E21" s="21" t="n"/>
+      <c r="D21" s="24" t="n"/>
+      <c r="E21" s="24" t="n"/>
       <c r="F21" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1644,14 +1642,14 @@
       <c r="G21" s="4" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1" s="19">
-      <c r="A22" s="24">
+      <c r="A22" s="23">
         <f>IF($A21="","",IF(MONTH($A21+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A21+1,""))</f>
         <v/>
       </c>
       <c r="B22" s="9" t="n"/>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="21" t="n"/>
-      <c r="E22" s="21" t="n"/>
+      <c r="D22" s="24" t="n"/>
+      <c r="E22" s="24" t="n"/>
       <c r="F22" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1660,14 +1658,14 @@
       <c r="G22" s="4" t="n"/>
     </row>
     <row r="23" ht="21" customHeight="1" s="19">
-      <c r="A23" s="24">
+      <c r="A23" s="23">
         <f>IF($A22="","",IF(MONTH($A22+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A22+1,""))</f>
         <v/>
       </c>
       <c r="B23" s="9" t="n"/>
       <c r="C23" s="8" t="n"/>
-      <c r="D23" s="21" t="n"/>
-      <c r="E23" s="21" t="n"/>
+      <c r="D23" s="24" t="n"/>
+      <c r="E23" s="24" t="n"/>
       <c r="F23" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1680,42 +1678,42 @@
         <f>IF($A23="","",IF(MONTH($A23+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A23+1,""))</f>
         <v/>
       </c>
-      <c r="B24" s="15" t="n"/>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="21" t="n"/>
-      <c r="E24" s="21" t="n"/>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="24" t="n"/>
+      <c r="E24" s="24" t="n"/>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n"/>
     </row>
     <row r="25" ht="21" customHeight="1" s="19">
       <c r="A25" s="23">
         <f>IF($A24="","",IF(MONTH($A24+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A24+1,""))</f>
         <v/>
       </c>
-      <c r="B25" s="15" t="n"/>
-      <c r="C25" s="14" t="n"/>
-      <c r="D25" s="21" t="n"/>
-      <c r="E25" s="21" t="n"/>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="24" t="n"/>
+      <c r="E25" s="24" t="n"/>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n"/>
     </row>
     <row r="26" ht="21" customHeight="1" s="19">
-      <c r="A26" s="24">
+      <c r="A26" s="23">
         <f>IF($A25="","",IF(MONTH($A25+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A25+1,""))</f>
         <v/>
       </c>
       <c r="B26" s="9" t="n"/>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="21" t="n"/>
-      <c r="E26" s="21" t="n"/>
+      <c r="D26" s="24" t="n"/>
+      <c r="E26" s="24" t="n"/>
       <c r="F26" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1724,14 +1722,14 @@
       <c r="G26" s="4" t="n"/>
     </row>
     <row r="27" ht="21" customHeight="1" s="19">
-      <c r="A27" s="24">
+      <c r="A27" s="23">
         <f>IF($A26="","",IF(MONTH($A26+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A26+1,""))</f>
         <v/>
       </c>
       <c r="B27" s="9" t="n"/>
       <c r="C27" s="8" t="n"/>
-      <c r="D27" s="21" t="n"/>
-      <c r="E27" s="21" t="n"/>
+      <c r="D27" s="24" t="n"/>
+      <c r="E27" s="24" t="n"/>
       <c r="F27" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1740,14 +1738,14 @@
       <c r="G27" s="4" t="n"/>
     </row>
     <row r="28" ht="21" customHeight="1" s="19">
-      <c r="A28" s="24">
+      <c r="A28" s="23">
         <f>IF($A27="","",IF(MONTH($A27+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A27+1,""))</f>
         <v/>
       </c>
       <c r="B28" s="9" t="n"/>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="21" t="n"/>
-      <c r="E28" s="21" t="n"/>
+      <c r="D28" s="24" t="n"/>
+      <c r="E28" s="24" t="n"/>
       <c r="F28" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1756,14 +1754,14 @@
       <c r="G28" s="4" t="n"/>
     </row>
     <row r="29" ht="21" customHeight="1" s="19">
-      <c r="A29" s="24">
+      <c r="A29" s="23">
         <f>IF($A28="","",IF(MONTH($A28+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A28+1,""))</f>
         <v/>
       </c>
       <c r="B29" s="9" t="n"/>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="21" t="n"/>
-      <c r="E29" s="21" t="n"/>
+      <c r="D29" s="24" t="n"/>
+      <c r="E29" s="24" t="n"/>
       <c r="F29" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1772,14 +1770,14 @@
       <c r="G29" s="4" t="n"/>
     </row>
     <row r="30" ht="21" customHeight="1" s="19">
-      <c r="A30" s="24">
+      <c r="A30" s="23">
         <f>IF($A29="","",IF(MONTH($A29+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A29+1,""))</f>
         <v/>
       </c>
       <c r="B30" s="9" t="n"/>
       <c r="C30" s="8" t="n"/>
-      <c r="D30" s="21" t="n"/>
-      <c r="E30" s="21" t="n"/>
+      <c r="D30" s="24" t="n"/>
+      <c r="E30" s="24" t="n"/>
       <c r="F30" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1792,42 +1790,42 @@
         <f>IF($A30="","",IF(MONTH($A30+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A30+1,""))</f>
         <v/>
       </c>
-      <c r="B31" s="15" t="n"/>
-      <c r="C31" s="14" t="n"/>
-      <c r="D31" s="21" t="n"/>
-      <c r="E31" s="21" t="n"/>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="G31" s="16" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="24" t="n"/>
+      <c r="E31" s="24" t="n"/>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n"/>
     </row>
     <row r="32" ht="21" customHeight="1" s="19">
       <c r="A32" s="23">
         <f>IF($A31="","",IF(MONTH($A31+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A31+1,""))</f>
         <v/>
       </c>
-      <c r="B32" s="15" t="n"/>
-      <c r="C32" s="14" t="n"/>
-      <c r="D32" s="21" t="n"/>
-      <c r="E32" s="21" t="n"/>
-      <c r="F32" s="16" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="n"/>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="24" t="n"/>
+      <c r="E32" s="24" t="n"/>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n"/>
     </row>
     <row r="33" ht="21" customHeight="1" s="19">
-      <c r="A33" s="24">
+      <c r="A33" s="23">
         <f>IF($A32="","",IF(MONTH($A32+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A32+1,""))</f>
         <v/>
       </c>
       <c r="B33" s="9" t="n"/>
       <c r="C33" s="8" t="n"/>
-      <c r="D33" s="21" t="n"/>
-      <c r="E33" s="21" t="n"/>
+      <c r="D33" s="24" t="n"/>
+      <c r="E33" s="24" t="n"/>
       <c r="F33" s="4" t="inlineStr">
         <is>
           <t>/</t>
@@ -1836,14 +1834,14 @@
       <c r="G33" s="4" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="24">
+      <c r="A34" s="23">
         <f>IF($A33="","",IF(MONTH($A33+1)=VALUE(SUBSTITUTE(SUBSTITUTE(LEFT($A$1,FIND("月度",$A$1)-1),"　","")," ","")),$A33+1,""))</f>
         <v/>
       </c>
       <c r="B34" s="9" t="n"/>
       <c r="C34" s="8" t="n"/>
-      <c r="D34" s="21" t="n"/>
-      <c r="E34" s="21" t="n"/>
+      <c r="D34" s="24" t="n"/>
+      <c r="E34" s="24" t="n"/>
       <c r="F34" s="4" t="inlineStr">
         <is>
           <t>/</t>
